--- a/artfynd/A 57229-2024 artfynd.xlsx
+++ b/artfynd/A 57229-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>649468</v>
       </c>
       <c r="B2" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475112.9378407548</v>
+        <v>475113</v>
       </c>
       <c r="R2" t="n">
-        <v>6237563.22481295</v>
+        <v>6237563</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2011-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +777,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3510578</v>
+        <v>1980437</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nybygden, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475112.9378407548</v>
+        <v>475113</v>
       </c>
       <c r="R3" t="n">
-        <v>6237563.22481295</v>
+        <v>6237563</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,24 +855,9 @@
           <t>2011-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammalt hamlingsspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,60 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1980437</v>
+        <v>3510578</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nybygden, Bl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475112.9378407548</v>
+        <v>475113</v>
       </c>
       <c r="R4" t="n">
-        <v>6237563.22481295</v>
+        <v>6237563</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,19 +957,14 @@
           <t>2011-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-09-26</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammalt hamlingsspår</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57229-2024 artfynd.xlsx
+++ b/artfynd/A 57229-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/649468</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1980437</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3510578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>